--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MISSOURI_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MISSOURI_2011.xlsx
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C73">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C111">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C136">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C457">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C501">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C687">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C754">
